--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/109.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/109.xlsx
@@ -426,13 +426,13 @@
         <v>-7.902530226106863</v>
       </c>
       <c r="E2">
-        <v>-26.10261533211237</v>
+        <v>-25.29156563733861</v>
       </c>
       <c r="F2">
-        <v>-4.065332461392084</v>
+        <v>-4.01674457138088</v>
       </c>
       <c r="G2">
-        <v>-16.85225542050814</v>
+        <v>-16.50928952373072</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.898973808504736</v>
       </c>
       <c r="E3">
-        <v>-26.40182519522117</v>
+        <v>-25.78168237918877</v>
       </c>
       <c r="F3">
-        <v>-3.962685314674184</v>
+        <v>-3.91600929662864</v>
       </c>
       <c r="G3">
-        <v>-16.43969026958585</v>
+        <v>-16.39530413026808</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.837617921649962</v>
       </c>
       <c r="E4">
-        <v>-27.34717131516641</v>
+        <v>-26.35497360313782</v>
       </c>
       <c r="F4">
-        <v>-3.878648270027577</v>
+        <v>-3.93159420094491</v>
       </c>
       <c r="G4">
-        <v>-16.51981374800006</v>
+        <v>-15.56199843621428</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.705432790463257</v>
       </c>
       <c r="E5">
-        <v>-27.16323375792285</v>
+        <v>-26.61895646694095</v>
       </c>
       <c r="F5">
-        <v>-4.04012358459009</v>
+        <v>-3.88864169437495</v>
       </c>
       <c r="G5">
-        <v>-16.5677785870458</v>
+        <v>-16.44647357739582</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.487127284927788</v>
       </c>
       <c r="E6">
-        <v>-27.48545279746463</v>
+        <v>-26.28398977306759</v>
       </c>
       <c r="F6">
-        <v>-4.022972237515126</v>
+        <v>-3.791698685592727</v>
       </c>
       <c r="G6">
-        <v>-16.64661260797246</v>
+        <v>-16.4328573035928</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.165757708682788</v>
       </c>
       <c r="E7">
-        <v>-27.67488339367949</v>
+        <v>-27.00640364608921</v>
       </c>
       <c r="F7">
-        <v>-3.867154672313734</v>
+        <v>-3.728600283786683</v>
       </c>
       <c r="G7">
-        <v>-16.40101813186886</v>
+        <v>-16.39040452286995</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.739531562608652</v>
       </c>
       <c r="E8">
-        <v>-28.2939665467941</v>
+        <v>-27.57745780387847</v>
       </c>
       <c r="F8">
-        <v>-3.988281867420689</v>
+        <v>-3.641407987702812</v>
       </c>
       <c r="G8">
-        <v>-16.33684817240839</v>
+        <v>-15.93007647617983</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.207847805048546</v>
       </c>
       <c r="E9">
-        <v>-28.81342327173995</v>
+        <v>-28.09225472907043</v>
       </c>
       <c r="F9">
-        <v>-3.748124903470667</v>
+        <v>-3.544351492586406</v>
       </c>
       <c r="G9">
-        <v>-16.55326018958332</v>
+        <v>-15.94871484756593</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.574502950750579</v>
       </c>
       <c r="E10">
-        <v>-28.93610416108175</v>
+        <v>-28.41589570945062</v>
       </c>
       <c r="F10">
-        <v>-3.884213242239584</v>
+        <v>-3.832871858981473</v>
       </c>
       <c r="G10">
-        <v>-16.28348052304257</v>
+        <v>-16.2968733350217</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.864873847964738</v>
       </c>
       <c r="E11">
-        <v>-29.40323889734299</v>
+        <v>-28.42182348192666</v>
       </c>
       <c r="F11">
-        <v>-3.764200201289394</v>
+        <v>-3.560281826109643</v>
       </c>
       <c r="G11">
-        <v>-15.84380200415366</v>
+        <v>-15.91725473330624</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.105087559657921</v>
       </c>
       <c r="E12">
-        <v>-30.63185012341602</v>
+        <v>-30.27537770648022</v>
       </c>
       <c r="F12">
-        <v>-3.600706155366259</v>
+        <v>-3.342537998977168</v>
       </c>
       <c r="G12">
-        <v>-15.77064556882684</v>
+        <v>-15.5809513094266</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.324482939371825</v>
       </c>
       <c r="E13">
-        <v>-30.72510046018196</v>
+        <v>-29.93154878897384</v>
       </c>
       <c r="F13">
-        <v>-3.53666838492544</v>
+        <v>-3.330820742064569</v>
       </c>
       <c r="G13">
-        <v>-15.55073099447137</v>
+        <v>-15.5201961776899</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.566978262917539</v>
       </c>
       <c r="E14">
-        <v>-31.3538224702219</v>
+        <v>-31.18986680453719</v>
       </c>
       <c r="F14">
-        <v>-3.423942492017678</v>
+        <v>-3.244918214026857</v>
       </c>
       <c r="G14">
-        <v>-15.15178211735211</v>
+        <v>-14.93765272132651</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.866966976437396</v>
       </c>
       <c r="E15">
-        <v>-32.60488813466196</v>
+        <v>-31.5407986335246</v>
       </c>
       <c r="F15">
-        <v>-3.359775496262023</v>
+        <v>-3.145008821575209</v>
       </c>
       <c r="G15">
-        <v>-14.62437910749081</v>
+        <v>-14.9590934695116</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.251359912776459</v>
       </c>
       <c r="E16">
-        <v>-32.75279715270049</v>
+        <v>-32.02602235920948</v>
       </c>
       <c r="F16">
-        <v>-2.970348383062336</v>
+        <v>-3.090135279711561</v>
       </c>
       <c r="G16">
-        <v>-14.67729817793606</v>
+        <v>-14.51077277149241</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.749149085419194</v>
       </c>
       <c r="E17">
-        <v>-33.46481817787451</v>
+        <v>-32.63847356213985</v>
       </c>
       <c r="F17">
-        <v>-3.179244417965509</v>
+        <v>-2.689755492712059</v>
       </c>
       <c r="G17">
-        <v>-14.03742765974188</v>
+        <v>-14.25119786157647</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.3728514032619127</v>
       </c>
       <c r="E18">
-        <v>-33.84045056833676</v>
+        <v>-32.93169904684751</v>
       </c>
       <c r="F18">
-        <v>-2.77511626846834</v>
+        <v>-2.555019049544511</v>
       </c>
       <c r="G18">
-        <v>-13.58501678270893</v>
+        <v>-13.63603725528741</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.1234592848175463</v>
       </c>
       <c r="E19">
-        <v>-34.85903343417105</v>
+        <v>-33.91258236656794</v>
       </c>
       <c r="F19">
-        <v>-2.596176483952605</v>
+        <v>-2.280713467781483</v>
       </c>
       <c r="G19">
-        <v>-13.66870240812339</v>
+        <v>-13.41064703860997</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.0006065974272849791</v>
       </c>
       <c r="E20">
-        <v>-34.81807112253466</v>
+        <v>-35.18863162210832</v>
       </c>
       <c r="F20">
-        <v>-2.708020993943788</v>
+        <v>-2.422969001864242</v>
       </c>
       <c r="G20">
-        <v>-13.40516477519694</v>
+        <v>-12.9311443121564</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.008406287845522753</v>
       </c>
       <c r="E21">
-        <v>-35.65499198931425</v>
+        <v>-35.17719948947596</v>
       </c>
       <c r="F21">
-        <v>-2.331812139390573</v>
+        <v>-2.134846251822518</v>
       </c>
       <c r="G21">
-        <v>-13.43046396420805</v>
+        <v>-13.17621075624649</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.07731160165908135</v>
       </c>
       <c r="E22">
-        <v>-35.84199532346099</v>
+        <v>-35.68616600438305</v>
       </c>
       <c r="F22">
-        <v>-2.191171921743273</v>
+        <v>-2.053777247580141</v>
       </c>
       <c r="G22">
-        <v>-12.96691144616268</v>
+        <v>-12.50729185621797</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.2404267948227772</v>
       </c>
       <c r="E23">
-        <v>-36.14606197494302</v>
+        <v>-35.6657697574525</v>
       </c>
       <c r="F23">
-        <v>-2.055157307673205</v>
+        <v>-2.246173860554355</v>
       </c>
       <c r="G23">
-        <v>-12.84049826474561</v>
+        <v>-12.18364630320774</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.4619450840628073</v>
       </c>
       <c r="E24">
-        <v>-36.82806827439421</v>
+        <v>-36.41476577289915</v>
       </c>
       <c r="F24">
-        <v>-2.107601247944442</v>
+        <v>-1.951299087812412</v>
       </c>
       <c r="G24">
-        <v>-12.94650855400415</v>
+        <v>-12.00173844691586</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.723313963222078</v>
       </c>
       <c r="E25">
-        <v>-37.35636684484005</v>
+        <v>-36.47250608073396</v>
       </c>
       <c r="F25">
-        <v>-1.927051117197665</v>
+        <v>-1.984237460849929</v>
       </c>
       <c r="G25">
-        <v>-12.7875825048459</v>
+        <v>-12.66612521010112</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.009839857725773</v>
       </c>
       <c r="E26">
-        <v>-37.47720917373473</v>
+        <v>-36.41431745397239</v>
       </c>
       <c r="F26">
-        <v>-1.623866162670837</v>
+        <v>-1.682319908449385</v>
       </c>
       <c r="G26">
-        <v>-12.77103639824062</v>
+        <v>-12.3557152181569</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.311813780276334</v>
       </c>
       <c r="E27">
-        <v>-37.52368037400144</v>
+        <v>-36.58778065083621</v>
       </c>
       <c r="F27">
-        <v>-1.737886793829175</v>
+        <v>-1.77755316691223</v>
       </c>
       <c r="G27">
-        <v>-12.52442723992923</v>
+        <v>-13.14088723534246</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.620564098530936</v>
       </c>
       <c r="E28">
-        <v>-37.43679254321627</v>
+        <v>-37.49361809930152</v>
       </c>
       <c r="F28">
-        <v>-1.984339350040473</v>
+        <v>-1.83764708014832</v>
       </c>
       <c r="G28">
-        <v>-12.67009786474825</v>
+        <v>-13.11398905283588</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.928976535233133</v>
       </c>
       <c r="E29">
-        <v>-37.71715489750515</v>
+        <v>-36.58847803583339</v>
       </c>
       <c r="F29">
-        <v>-1.864549968289039</v>
+        <v>-1.826850967787634</v>
       </c>
       <c r="G29">
-        <v>-12.70976151085425</v>
+        <v>-12.71365471240844</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.235179790952775</v>
       </c>
       <c r="E30">
-        <v>-37.20429389495146</v>
+        <v>-37.02210885714888</v>
       </c>
       <c r="F30">
-        <v>-1.836257908013825</v>
+        <v>-1.634191762346733</v>
       </c>
       <c r="G30">
-        <v>-13.23813451055855</v>
+        <v>-12.47656668306799</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.535350205333139</v>
       </c>
       <c r="E31">
-        <v>-36.86021817561166</v>
+        <v>-36.12483701726907</v>
       </c>
       <c r="F31">
-        <v>-2.033750637250061</v>
+        <v>-1.93950396436395</v>
       </c>
       <c r="G31">
-        <v>-12.65131382935842</v>
+        <v>-13.20309900711645</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.824349933284378</v>
       </c>
       <c r="E32">
-        <v>-36.69581192676319</v>
+        <v>-36.11137159980726</v>
       </c>
       <c r="F32">
-        <v>-1.831120373381663</v>
+        <v>-2.009762773999793</v>
       </c>
       <c r="G32">
-        <v>-12.93860297125637</v>
+        <v>-12.48781922735597</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.101860904860237</v>
       </c>
       <c r="E33">
-        <v>-37.06797097766156</v>
+        <v>-36.7142994218995</v>
       </c>
       <c r="F33">
-        <v>-2.011267089203276</v>
+        <v>-2.059420914695415</v>
       </c>
       <c r="G33">
-        <v>-13.35118964072466</v>
+        <v>-12.673828849571</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.364596770391573</v>
       </c>
       <c r="E34">
-        <v>-36.2159476500664</v>
+        <v>-35.31924639791156</v>
       </c>
       <c r="F34">
-        <v>-1.971276824465728</v>
+        <v>-1.964927388323269</v>
       </c>
       <c r="G34">
-        <v>-13.20796550905917</v>
+        <v>-13.00433716348414</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.608535078592428</v>
       </c>
       <c r="E35">
-        <v>-35.83130359632889</v>
+        <v>-35.23227252612024</v>
       </c>
       <c r="F35">
-        <v>-1.891641724197597</v>
+        <v>-1.821012634332703</v>
       </c>
       <c r="G35">
-        <v>-13.46949529611606</v>
+        <v>-13.03438698534411</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.833577704572377</v>
       </c>
       <c r="E36">
-        <v>-35.21522508571837</v>
+        <v>-35.51041592814536</v>
       </c>
       <c r="F36">
-        <v>-2.07827704188534</v>
+        <v>-2.019335387706544</v>
       </c>
       <c r="G36">
-        <v>-12.95913828523647</v>
+        <v>-12.63846891266605</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.035790943788474</v>
       </c>
       <c r="E37">
-        <v>-35.38660744877566</v>
+        <v>-34.43372594808166</v>
       </c>
       <c r="F37">
-        <v>-2.066075190042103</v>
+        <v>-1.850123121601883</v>
       </c>
       <c r="G37">
-        <v>-13.23853177602327</v>
+        <v>-13.31150282079988</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.211624981767227</v>
       </c>
       <c r="E38">
-        <v>-35.13119019355803</v>
+        <v>-33.9973372860955</v>
       </c>
       <c r="F38">
-        <v>-2.100261084388236</v>
+        <v>-1.891450371327551</v>
       </c>
       <c r="G38">
-        <v>-13.58947608755033</v>
+        <v>-13.44607318642572</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.361362938879559</v>
       </c>
       <c r="E39">
-        <v>-34.51471770570884</v>
+        <v>-33.31577251286006</v>
       </c>
       <c r="F39">
-        <v>-1.978352738820441</v>
+        <v>-1.808249149390368</v>
       </c>
       <c r="G39">
-        <v>-13.50266696241956</v>
+        <v>-13.10239552235736</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.483221442164593</v>
       </c>
       <c r="E40">
-        <v>-34.29867779622491</v>
+        <v>-33.54866513836354</v>
       </c>
       <c r="F40">
-        <v>-1.968473629174654</v>
+        <v>-1.615435039245144</v>
       </c>
       <c r="G40">
-        <v>-13.30651713921774</v>
+        <v>-12.87089238334166</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.577907856362629</v>
       </c>
       <c r="E41">
-        <v>-33.75080489688092</v>
+        <v>-33.06431087968814</v>
       </c>
       <c r="F41">
-        <v>-1.937687354649611</v>
+        <v>-1.913425301789016</v>
       </c>
       <c r="G41">
-        <v>-13.09679076875937</v>
+        <v>-12.81872480673383</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.650079361208928</v>
       </c>
       <c r="E42">
-        <v>-32.75370058326502</v>
+        <v>-32.19390421185884</v>
       </c>
       <c r="F42">
-        <v>-2.023526926764709</v>
+        <v>-1.77899121272349</v>
       </c>
       <c r="G42">
-        <v>-13.77495933302461</v>
+        <v>-12.65843150226785</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.702409177297443</v>
       </c>
       <c r="E43">
-        <v>-33.50250866704036</v>
+        <v>-32.10376267249915</v>
       </c>
       <c r="F43">
-        <v>-2.009812476043961</v>
+        <v>-1.501014306631254</v>
       </c>
       <c r="G43">
-        <v>-13.0801188614236</v>
+        <v>-12.73747739810903</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.740342130316401</v>
       </c>
       <c r="E44">
-        <v>-32.41183023076696</v>
+        <v>-31.55864761382583</v>
       </c>
       <c r="F44">
-        <v>-1.88219170886646</v>
+        <v>-1.694274078439184</v>
       </c>
       <c r="G44">
-        <v>-13.26106334896355</v>
+        <v>-13.15172596143804</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.771693059766188</v>
       </c>
       <c r="E45">
-        <v>-32.00602008951759</v>
+        <v>-30.85542994212272</v>
       </c>
       <c r="F45">
-        <v>-1.874120096893582</v>
+        <v>-1.756179631185197</v>
       </c>
       <c r="G45">
-        <v>-13.3504679417971</v>
+        <v>-13.04385514558642</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.801506862420221</v>
       </c>
       <c r="E46">
-        <v>-31.17073400185478</v>
+        <v>-31.14048832395755</v>
       </c>
       <c r="F46">
-        <v>-1.937766049552876</v>
+        <v>-1.63550472468017</v>
       </c>
       <c r="G46">
-        <v>-12.95446710548056</v>
+        <v>-13.31801135333009</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.837577347352853</v>
       </c>
       <c r="E47">
-        <v>-30.78392760177861</v>
+        <v>-30.79818550219176</v>
       </c>
       <c r="F47">
-        <v>-1.858529394005493</v>
+        <v>-1.724527712724228</v>
       </c>
       <c r="G47">
-        <v>-13.26044096640216</v>
+        <v>-13.36223693118921</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.888452241084695</v>
       </c>
       <c r="E48">
-        <v>-30.08675317863873</v>
+        <v>-30.98141208901611</v>
       </c>
       <c r="F48">
-        <v>-1.821939577456436</v>
+        <v>-1.664257357231341</v>
       </c>
       <c r="G48">
-        <v>-13.3537387607899</v>
+        <v>-12.88701805066345</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.957960744712073</v>
       </c>
       <c r="E49">
-        <v>-30.21269909774006</v>
+        <v>-29.40757264696833</v>
       </c>
       <c r="F49">
-        <v>-1.823506020215129</v>
+        <v>-1.634686297686204</v>
       </c>
       <c r="G49">
-        <v>-13.35277208149244</v>
+        <v>-13.25284657493508</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.051153095185823</v>
       </c>
       <c r="E50">
-        <v>-29.70037924783028</v>
+        <v>-28.87611999437615</v>
       </c>
       <c r="F50">
-        <v>-1.895060396468951</v>
+        <v>-1.788526549897115</v>
       </c>
       <c r="G50">
-        <v>-13.13543145629374</v>
+        <v>-12.9879201681549</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.172353129789499</v>
       </c>
       <c r="E51">
-        <v>-29.01879409646181</v>
+        <v>-28.96013224416645</v>
       </c>
       <c r="F51">
-        <v>-1.97327484664128</v>
+        <v>-1.650165170974916</v>
       </c>
       <c r="G51">
-        <v>-13.55444389465376</v>
+        <v>-13.4768413966677</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.32056258898298</v>
       </c>
       <c r="E52">
-        <v>-29.28469250477019</v>
+        <v>-27.70073645178928</v>
       </c>
       <c r="F52">
-        <v>-1.623777527358738</v>
+        <v>-1.531024400899874</v>
       </c>
       <c r="G52">
-        <v>-13.21967490863158</v>
+        <v>-13.19489216472459</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.496538945899619</v>
       </c>
       <c r="E53">
-        <v>-28.59650483829854</v>
+        <v>-27.57199193575121</v>
       </c>
       <c r="F53">
-        <v>-1.836801317030061</v>
+        <v>-1.553489724863797</v>
       </c>
       <c r="G53">
-        <v>-13.24482181254788</v>
+        <v>-13.05357490728972</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.700405586098683</v>
       </c>
       <c r="E54">
-        <v>-28.03897723237019</v>
+        <v>-27.7486295928944</v>
       </c>
       <c r="F54">
-        <v>-1.821210614141972</v>
+        <v>-1.279897367434579</v>
       </c>
       <c r="G54">
-        <v>-13.39041629481949</v>
+        <v>-13.18492080156031</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.926806169419662</v>
       </c>
       <c r="E55">
-        <v>-27.7268476329175</v>
+        <v>-27.05638441371187</v>
       </c>
       <c r="F55">
-        <v>-1.752021226823143</v>
+        <v>-1.67737124158506</v>
       </c>
       <c r="G55">
-        <v>-13.31753463477243</v>
+        <v>-13.38051114256599</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.172790478753795</v>
       </c>
       <c r="E56">
-        <v>-27.32561125041589</v>
+        <v>-26.56696505685889</v>
       </c>
       <c r="F56">
-        <v>-1.750651107138913</v>
+        <v>-1.741941652265879</v>
       </c>
       <c r="G56">
-        <v>-13.70108450931578</v>
+        <v>-13.18431166118108</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.435049378273333</v>
       </c>
       <c r="E57">
-        <v>-27.1133752590984</v>
+        <v>-26.77595866078688</v>
       </c>
       <c r="F57">
-        <v>-1.872872575584966</v>
+        <v>-1.459009452370096</v>
       </c>
       <c r="G57">
-        <v>-13.70737454584039</v>
+        <v>-13.59096086722469</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.705485346103425</v>
       </c>
       <c r="E58">
-        <v>-26.77544241475001</v>
+        <v>-26.02573542888415</v>
       </c>
       <c r="F58">
-        <v>-2.03782206303482</v>
+        <v>-1.822771258328846</v>
       </c>
       <c r="G58">
-        <v>-14.00579374184137</v>
+        <v>-13.79900879109465</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.979789983338292</v>
       </c>
       <c r="E59">
-        <v>-26.5210418019471</v>
+        <v>-26.01499388853796</v>
       </c>
       <c r="F59">
-        <v>-2.042874275824495</v>
+        <v>-1.787702324331329</v>
       </c>
       <c r="G59">
-        <v>-14.02105866732295</v>
+        <v>-13.48257195099618</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.253096782534387</v>
       </c>
       <c r="E60">
-        <v>-26.2136263439364</v>
+        <v>-25.08973607929075</v>
       </c>
       <c r="F60">
-        <v>-2.010116486880788</v>
+        <v>-1.864018984783845</v>
       </c>
       <c r="G60">
-        <v>-14.00890565464829</v>
+        <v>-14.11065196125225</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.516008355754722</v>
       </c>
       <c r="E61">
-        <v>-26.22682684566876</v>
+        <v>-25.3465820680578</v>
       </c>
       <c r="F61">
-        <v>-1.897925719315234</v>
+        <v>-1.791330573555591</v>
       </c>
       <c r="G61">
-        <v>-13.95088503352702</v>
+        <v>-13.94779463926611</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.764399993962783</v>
       </c>
       <c r="E62">
-        <v>-25.49386162820926</v>
+        <v>-25.0679812901579</v>
       </c>
       <c r="F62">
-        <v>-2.17102022793537</v>
+        <v>-2.015188580488129</v>
       </c>
       <c r="G62">
-        <v>-13.83780838481491</v>
+        <v>-13.98481978057732</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.99412181239665</v>
       </c>
       <c r="E63">
-        <v>-25.62881468211184</v>
+        <v>-25.18758734564849</v>
       </c>
       <c r="F63">
-        <v>-2.208281850448097</v>
+        <v>-1.998815898771797</v>
       </c>
       <c r="G63">
-        <v>-14.23038115122553</v>
+        <v>-14.35135841686712</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.197891685470282</v>
       </c>
       <c r="E64">
-        <v>-25.23619598564682</v>
+        <v>-24.61089070924568</v>
       </c>
       <c r="F64">
-        <v>-2.111951833543945</v>
+        <v>-2.124794841756949</v>
       </c>
       <c r="G64">
-        <v>-14.46205974915481</v>
+        <v>-13.97813082331522</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.374242894533205</v>
       </c>
       <c r="E65">
-        <v>-25.29532427076498</v>
+        <v>-24.93200480112958</v>
       </c>
       <c r="F65">
-        <v>-2.184496937211515</v>
+        <v>-2.119156973213495</v>
       </c>
       <c r="G65">
-        <v>-14.24458670213454</v>
+        <v>-14.40882286633779</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.520590012829876</v>
       </c>
       <c r="E66">
-        <v>-24.51740942030534</v>
+        <v>-24.10525035849722</v>
       </c>
       <c r="F66">
-        <v>-2.320832957833868</v>
+        <v>-2.250161621231431</v>
       </c>
       <c r="G66">
-        <v>-14.52902215377765</v>
+        <v>-14.41063870056608</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.632124004456861</v>
       </c>
       <c r="E67">
-        <v>-24.67116922676178</v>
+        <v>-24.19203856285423</v>
       </c>
       <c r="F67">
-        <v>-2.540848996752223</v>
+        <v>-2.115026733343137</v>
       </c>
       <c r="G67">
-        <v>-14.27911569210914</v>
+        <v>-13.91217813508186</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.709988005853456</v>
       </c>
       <c r="E68">
-        <v>-25.41046977935801</v>
+        <v>-24.19682063140633</v>
       </c>
       <c r="F68">
-        <v>-2.405375306596183</v>
+        <v>-2.213849307762313</v>
       </c>
       <c r="G68">
-        <v>-14.2456195923428</v>
+        <v>-14.62931016507156</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.753140361461178</v>
       </c>
       <c r="E69">
-        <v>-24.98459396978066</v>
+        <v>-23.98043655789781</v>
       </c>
       <c r="F69">
-        <v>-2.642164957053825</v>
+        <v>-2.401943380446385</v>
       </c>
       <c r="G69">
-        <v>-14.23495466988803</v>
+        <v>-14.6806434842035</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.759641032527975</v>
       </c>
       <c r="E70">
-        <v>-24.93519284683098</v>
+        <v>-24.54849286589399</v>
       </c>
       <c r="F70">
-        <v>-2.704315706551066</v>
+        <v>-2.441497923930061</v>
       </c>
       <c r="G70">
-        <v>-14.27322292104924</v>
+        <v>-13.97856119423533</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.732416655558135</v>
       </c>
       <c r="E71">
-        <v>-24.84013112046197</v>
+        <v>-23.68100027108862</v>
       </c>
       <c r="F71">
-        <v>-2.744122902092597</v>
+        <v>-2.660145499898991</v>
       </c>
       <c r="G71">
-        <v>-14.13079332031318</v>
+        <v>-13.85536420780966</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.669915460916513</v>
       </c>
       <c r="E72">
-        <v>-24.66338477994259</v>
+        <v>-23.82878702032895</v>
       </c>
       <c r="F72">
-        <v>-2.798812546392822</v>
+        <v>-2.712343415051596</v>
       </c>
       <c r="G72">
-        <v>-14.34451220869191</v>
+        <v>-14.01989832111144</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.571296487317126</v>
       </c>
       <c r="E73">
-        <v>-24.59776266309744</v>
+        <v>-24.21984339326132</v>
       </c>
       <c r="F73">
-        <v>-2.749223988559036</v>
+        <v>-2.483882170461701</v>
       </c>
       <c r="G73">
-        <v>-13.98689383735767</v>
+        <v>-14.08868814687196</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.439829299188791</v>
       </c>
       <c r="E74">
-        <v>-25.32250870023302</v>
+        <v>-24.56582333592134</v>
       </c>
       <c r="F74">
-        <v>-2.960336734632101</v>
+        <v>-2.841581155399361</v>
       </c>
       <c r="G74">
-        <v>-13.92515216305027</v>
+        <v>-14.05953879339867</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.273741388129558</v>
       </c>
       <c r="E75">
-        <v>-25.22556312867681</v>
+        <v>-24.340092492061</v>
       </c>
       <c r="F75">
-        <v>-3.000425575090583</v>
+        <v>-2.782064614243022</v>
       </c>
       <c r="G75">
-        <v>-13.64836076105734</v>
+        <v>-13.84989187603325</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.07429047559061</v>
       </c>
       <c r="E76">
-        <v>-25.12203315591345</v>
+        <v>-24.63565693359363</v>
       </c>
       <c r="F76">
-        <v>-3.14732907867045</v>
+        <v>-2.81470726011774</v>
       </c>
       <c r="G76">
-        <v>-14.15464580092362</v>
+        <v>-13.28368099608785</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.846877856724058</v>
       </c>
       <c r="E77">
-        <v>-25.25965348100656</v>
+        <v>-25.40410274490323</v>
       </c>
       <c r="F77">
-        <v>-3.115335044472125</v>
+        <v>-2.817455783160228</v>
       </c>
       <c r="G77">
-        <v>-13.93711150881088</v>
+        <v>-13.97377414538554</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.592208390519788</v>
       </c>
       <c r="E78">
-        <v>-25.97715395972986</v>
+        <v>-25.61371222129626</v>
       </c>
       <c r="F78">
-        <v>-3.356388301951975</v>
+        <v>-2.919481654326029</v>
       </c>
       <c r="G78">
-        <v>-13.53840264624322</v>
+        <v>-13.34499892056623</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.315547661677273</v>
       </c>
       <c r="E79">
-        <v>-26.24935600385692</v>
+        <v>-25.71372809822967</v>
       </c>
       <c r="F79">
-        <v>-3.169290755253471</v>
+        <v>-3.060973433663407</v>
       </c>
       <c r="G79">
-        <v>-13.12586729023079</v>
+        <v>-13.23668780215789</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.026151968266368</v>
       </c>
       <c r="E80">
-        <v>-26.79642736330155</v>
+        <v>-25.75683464230869</v>
       </c>
       <c r="F80">
-        <v>-3.17948712961453</v>
+        <v>-3.323433361566403</v>
       </c>
       <c r="G80">
-        <v>-13.26451624796101</v>
+        <v>-13.12144440139032</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.729258290206642</v>
       </c>
       <c r="E81">
-        <v>-26.97793313000299</v>
+        <v>-26.07295835583614</v>
       </c>
       <c r="F81">
-        <v>-3.32517541821449</v>
+        <v>-3.159135799262552</v>
       </c>
       <c r="G81">
-        <v>-12.92303678613072</v>
+        <v>-13.16358102501417</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.435612562444475</v>
       </c>
       <c r="E82">
-        <v>-27.11184463488381</v>
+        <v>-27.00898487627358</v>
       </c>
       <c r="F82">
-        <v>-3.218933156968439</v>
+        <v>-3.322067383719186</v>
       </c>
       <c r="G82">
-        <v>-12.86155333437538</v>
+        <v>-12.46093759757709</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.160650924506085</v>
       </c>
       <c r="E83">
-        <v>-28.30838520803452</v>
+        <v>-27.70097646091169</v>
       </c>
       <c r="F83">
-        <v>-3.211173839506416</v>
+        <v>-3.272987443470718</v>
       </c>
       <c r="G83">
-        <v>-12.39182995944481</v>
+        <v>-12.60111271680091</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.915189229259466</v>
       </c>
       <c r="E84">
-        <v>-28.83333044347767</v>
+        <v>-27.8239064163239</v>
       </c>
       <c r="F84">
-        <v>-3.571950209345477</v>
+        <v>-3.157129493412971</v>
       </c>
       <c r="G84">
-        <v>-12.43312239395614</v>
+        <v>-12.48900440265903</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.712788842235824</v>
       </c>
       <c r="E85">
-        <v>-28.83584374655193</v>
+        <v>-29.20734616871918</v>
       </c>
       <c r="F85">
-        <v>-3.563788305325693</v>
+        <v>-3.420918122630057</v>
       </c>
       <c r="G85">
-        <v>-12.69594329377334</v>
+        <v>-12.28379030577069</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.569360754679114</v>
       </c>
       <c r="E86">
-        <v>-29.9084422503497</v>
+        <v>-29.31740167252759</v>
       </c>
       <c r="F86">
-        <v>-3.780930737723736</v>
+        <v>-3.481024461377189</v>
       </c>
       <c r="G86">
-        <v>-12.29592014462658</v>
+        <v>-12.47995668170021</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.492144515489046</v>
       </c>
       <c r="E87">
-        <v>-31.08551264950443</v>
+        <v>-30.64137576849115</v>
       </c>
       <c r="F87">
-        <v>-3.696022250569384</v>
+        <v>-3.512973763735763</v>
       </c>
       <c r="G87">
-        <v>-12.22751103160308</v>
+        <v>-12.51464457786069</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.486041947686869</v>
       </c>
       <c r="E88">
-        <v>-31.34727882528081</v>
+        <v>-31.46226130880957</v>
       </c>
       <c r="F88">
-        <v>-3.812710224764736</v>
+        <v>-3.713475123378966</v>
       </c>
       <c r="G88">
-        <v>-12.14190694504861</v>
+        <v>-12.32306661804861</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.557828640983322</v>
       </c>
       <c r="E89">
-        <v>-32.81210657677895</v>
+        <v>-32.59062797001181</v>
       </c>
       <c r="F89">
-        <v>-3.979220356401465</v>
+        <v>-3.587495352026412</v>
       </c>
       <c r="G89">
-        <v>-12.58361648362587</v>
+        <v>-11.45466086491468</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.704040920876388</v>
       </c>
       <c r="E90">
-        <v>-33.61243963781356</v>
+        <v>-32.98344139085916</v>
       </c>
       <c r="F90">
-        <v>-3.838276127917337</v>
+        <v>-3.852979649317029</v>
       </c>
       <c r="G90">
-        <v>-12.40491985650709</v>
+        <v>-12.24588786989158</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.91704907003142</v>
       </c>
       <c r="E91">
-        <v>-34.94710319667222</v>
+        <v>-34.34327194401545</v>
       </c>
       <c r="F91">
-        <v>-4.260659009869999</v>
+        <v>-3.793911254925604</v>
       </c>
       <c r="G91">
-        <v>-12.39589861991257</v>
+        <v>-11.87765588955844</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.193454105706218</v>
       </c>
       <c r="E92">
-        <v>-36.16144746538409</v>
+        <v>-36.59575982203772</v>
       </c>
       <c r="F92">
-        <v>-4.153024263019844</v>
+        <v>-3.875405211645617</v>
       </c>
       <c r="G92">
-        <v>-12.4158545884233</v>
+        <v>-12.63797233083516</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.520243956345573</v>
       </c>
       <c r="E93">
-        <v>-37.30417618190165</v>
+        <v>-37.62859832404816</v>
       </c>
       <c r="F93">
-        <v>-4.00013000638293</v>
+        <v>-4.101662170576662</v>
       </c>
       <c r="G93">
-        <v>-12.45600819526912</v>
+        <v>-12.46303979399453</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.879895721818404</v>
       </c>
       <c r="E94">
-        <v>-38.85449699419059</v>
+        <v>-38.86196671206624</v>
       </c>
       <c r="F94">
-        <v>-3.988482332332166</v>
+        <v>-4.150439756723109</v>
       </c>
       <c r="G94">
-        <v>-12.72960823136219</v>
+        <v>-12.65128072390303</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.261528095681545</v>
       </c>
       <c r="E95">
-        <v>-40.17749520400549</v>
+        <v>-39.8533198636924</v>
       </c>
       <c r="F95">
-        <v>-4.456369092455411</v>
+        <v>-4.121935634392778</v>
       </c>
       <c r="G95">
-        <v>-12.65279695376002</v>
+        <v>-12.73680535736456</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.644134750852412</v>
       </c>
       <c r="E96">
-        <v>-41.18230698038245</v>
+        <v>-42.25443225864642</v>
       </c>
       <c r="F96">
-        <v>-4.362582991845256</v>
+        <v>-4.476334403597685</v>
       </c>
       <c r="G96">
-        <v>-13.15416914404602</v>
+        <v>-12.56019768448106</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.005774740457905</v>
       </c>
       <c r="E97">
-        <v>-43.51034339027469</v>
+        <v>-43.60443828744307</v>
       </c>
       <c r="F97">
-        <v>-4.531823422441613</v>
+        <v>-4.641855464555471</v>
       </c>
       <c r="G97">
-        <v>-13.21019681675264</v>
+        <v>-12.95513914622503</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.330069375970787</v>
       </c>
       <c r="E98">
-        <v>-45.16925248079356</v>
+        <v>-45.3770913238496</v>
       </c>
       <c r="F98">
-        <v>-4.601774079403614</v>
+        <v>-4.65167327501345</v>
       </c>
       <c r="G98">
-        <v>-13.55075760219578</v>
+        <v>-13.55228045314384</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.599739152711015</v>
       </c>
       <c r="E99">
-        <v>-47.04997981363015</v>
+        <v>-46.42493945295845</v>
       </c>
       <c r="F99">
-        <v>-4.572646196418975</v>
+        <v>-4.496118302278745</v>
       </c>
       <c r="G99">
-        <v>-13.51258866740075</v>
+        <v>-13.61884724757474</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.790504874315371</v>
       </c>
       <c r="E100">
-        <v>-48.45055984014446</v>
+        <v>-48.8858163836287</v>
       </c>
       <c r="F100">
-        <v>-4.767867542236734</v>
+        <v>-4.974420954124791</v>
       </c>
       <c r="G100">
-        <v>-13.56054357480986</v>
+        <v>-14.51236348862403</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.902736738379168</v>
       </c>
       <c r="E101">
-        <v>-50.25928670049609</v>
+        <v>-50.02419097238788</v>
       </c>
       <c r="F101">
-        <v>-4.921104742978406</v>
+        <v>-4.906129517070597</v>
       </c>
       <c r="G101">
-        <v>-14.27252936175876</v>
+        <v>-13.9175511504921</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.911870907627062</v>
       </c>
       <c r="E102">
-        <v>-52.03704106287226</v>
+        <v>-52.45905408412107</v>
       </c>
       <c r="F102">
-        <v>-5.02322587639553</v>
+        <v>-4.994725895902213</v>
       </c>
       <c r="G102">
-        <v>-13.99194241930506</v>
+        <v>-14.34564441526634</v>
       </c>
     </row>
   </sheetData>
